--- a/data/matrix_codebook.xlsx
+++ b/data/matrix_codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="627" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED5E2931-7813-4955-B178-FB33B5BAFE3F}"/>
+  <xr:revisionPtr revIDLastSave="645" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B42DEA66-79EC-497D-A3A4-7A12D4D2B6DD}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="391">
   <si>
     <t>BESSI</t>
   </si>
@@ -1206,6 +1206,12 @@
   </si>
   <si>
     <t>Academic Satisfaction</t>
+  </si>
+  <si>
+    <t>academicburnout</t>
+  </si>
+  <si>
+    <t>Academic Burnout</t>
   </si>
 </sst>
 </file>
@@ -1533,14 +1539,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A8B26-530C-40CA-A676-99F1EAC2BADD}">
-  <dimension ref="A1:AO185"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AO186"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="35.81640625" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="35.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -1557,7 +1563,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -1608,7 +1614,7 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -1622,7 +1628,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -1636,7 +1642,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1650,7 +1656,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1664,7 +1670,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1678,7 +1684,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -1692,7 +1698,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -1706,7 +1712,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -1720,7 +1726,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -1734,7 +1740,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -1748,7 +1754,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -1762,7 +1768,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -1776,7 +1782,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1790,7 +1796,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -1804,7 +1810,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -1818,7 +1824,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>82</v>
       </c>
@@ -1832,7 +1838,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -1846,7 +1852,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>82</v>
       </c>
@@ -1860,7 +1866,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>82</v>
       </c>
@@ -1874,7 +1880,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -1888,7 +1894,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -1902,7 +1908,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -1916,7 +1922,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -1930,7 +1936,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -1944,7 +1950,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -1958,7 +1964,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -1972,7 +1978,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -1986,7 +1992,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -2000,7 +2006,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>82</v>
       </c>
@@ -2014,7 +2020,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>82</v>
       </c>
@@ -2028,7 +2034,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -2042,7 +2048,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -2056,7 +2062,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2070,7 +2076,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -2084,7 +2090,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2098,7 +2104,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -2112,7 +2118,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -2165,7 +2171,7 @@
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -2182,7 +2188,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -2199,7 +2205,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -2216,7 +2222,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2233,12 +2239,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>328</v>
       </c>
@@ -2252,7 +2258,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>328</v>
       </c>
@@ -2266,7 +2272,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>328</v>
       </c>
@@ -2280,7 +2286,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>328</v>
       </c>
@@ -2294,7 +2300,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>328</v>
       </c>
@@ -2308,7 +2314,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>328</v>
       </c>
@@ -2322,7 +2328,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>328</v>
       </c>
@@ -2336,7 +2342,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>328</v>
       </c>
@@ -2350,7 +2356,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>328</v>
       </c>
@@ -2364,7 +2370,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>328</v>
       </c>
@@ -2378,7 +2384,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>328</v>
       </c>
@@ -2392,7 +2398,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>328</v>
       </c>
@@ -2406,7 +2412,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>328</v>
       </c>
@@ -2420,7 +2426,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>328</v>
       </c>
@@ -2434,7 +2440,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>328</v>
       </c>
@@ -2448,7 +2454,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>328</v>
       </c>
@@ -2462,7 +2468,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>328</v>
       </c>
@@ -2476,7 +2482,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>328</v>
       </c>
@@ -2490,7 +2496,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>328</v>
       </c>
@@ -2504,7 +2510,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>328</v>
       </c>
@@ -2518,7 +2524,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>328</v>
       </c>
@@ -2532,7 +2538,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>328</v>
       </c>
@@ -2546,14 +2552,14 @@
         <v>386</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B68" s="2"/>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2567,7 +2573,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2581,7 +2587,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2595,7 +2601,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2609,7 +2615,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2623,7 +2629,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2637,7 +2643,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2651,7 +2657,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2665,7 +2671,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2679,7 +2685,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2693,7 +2699,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2707,7 +2713,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2721,7 +2727,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2735,7 +2741,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -2749,7 +2755,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2763,7 +2769,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -2777,7 +2783,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -2791,7 +2797,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -2805,7 +2811,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -2819,7 +2825,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -2833,13 +2839,13 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>83</v>
       </c>
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -2853,7 +2859,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -2867,7 +2873,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -2881,7 +2887,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -2895,7 +2901,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -2909,7 +2915,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -2923,7 +2929,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -2931,7 +2937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -2945,7 +2951,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -2959,7 +2965,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -2973,7 +2979,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -2987,7 +2993,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3001,7 +3007,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3015,7 +3021,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3029,7 +3035,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3043,7 +3049,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>83</v>
       </c>
@@ -3057,7 +3063,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -3071,7 +3077,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>83</v>
       </c>
@@ -3085,7 +3091,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>83</v>
       </c>
@@ -3099,7 +3105,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>83</v>
       </c>
@@ -3113,7 +3119,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>83</v>
       </c>
@@ -3127,7 +3133,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>83</v>
       </c>
@@ -3141,18 +3147,18 @@
         <v>266</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B113" s="2"/>
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B114" s="2"/>
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B115" s="2"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>84</v>
       </c>
@@ -3169,7 +3175,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>84</v>
       </c>
@@ -3183,7 +3189,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>84</v>
       </c>
@@ -3200,7 +3206,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>84</v>
       </c>
@@ -3214,7 +3220,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>84</v>
       </c>
@@ -3228,7 +3234,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>84</v>
       </c>
@@ -3242,7 +3248,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>84</v>
       </c>
@@ -3256,7 +3262,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>84</v>
       </c>
@@ -3269,8 +3275,9 @@
       <c r="D123" s="1" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G123" s="2"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>84</v>
       </c>
@@ -3284,7 +3291,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>84</v>
       </c>
@@ -3297,8 +3304,9 @@
       <c r="D125" s="1" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="J125" s="2"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>84</v>
       </c>
@@ -3312,7 +3320,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>84</v>
       </c>
@@ -3326,21 +3334,21 @@
         <v>388</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>84</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>364</v>
+        <v>15</v>
       </c>
       <c r="C128" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>84</v>
       </c>
@@ -3348,44 +3356,44 @@
         <v>364</v>
       </c>
       <c r="C129" t="s">
+        <v>365</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>84</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C130" t="s">
         <v>367</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D130" s="1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B130" s="2"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>85</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C131" t="s">
-        <v>52</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B131" s="2"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>85</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>85</v>
       </c>
@@ -3393,27 +3401,27 @@
         <v>13</v>
       </c>
       <c r="C133" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>85</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>85</v>
       </c>
@@ -3421,78 +3429,78 @@
         <v>68</v>
       </c>
       <c r="C135" t="s">
+        <v>66</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>85</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C136" t="s">
         <v>67</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B136" s="2"/>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>86</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C137" t="s">
-        <v>54</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E137" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B137" s="2"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>86</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="C138" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+        <v>276</v>
+      </c>
+      <c r="E138" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>86</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C139" t="s">
+        <v>79</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>86</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C140" t="s">
         <v>345</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B140" s="2"/>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>87</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C141" t="s">
-        <v>58</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B141" s="2"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>87</v>
       </c>
@@ -3500,13 +3508,13 @@
         <v>57</v>
       </c>
       <c r="C142" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>87</v>
       </c>
@@ -3514,13 +3522,13 @@
         <v>57</v>
       </c>
       <c r="C143" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>87</v>
       </c>
@@ -3528,13 +3536,13 @@
         <v>57</v>
       </c>
       <c r="C144" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>87</v>
       </c>
@@ -3542,48 +3550,48 @@
         <v>57</v>
       </c>
       <c r="C145" t="s">
-        <v>356</v>
+        <v>61</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>87</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C146" t="s">
+        <v>356</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>87</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" t="s">
         <v>313</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D147" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B147" s="2"/>
-      <c r="D147" s="1"/>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B148" s="2"/>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>88</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C149" t="s">
-        <v>107</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D148" s="1"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B149" s="2"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>88</v>
       </c>
@@ -3591,13 +3599,13 @@
         <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>88</v>
       </c>
@@ -3605,13 +3613,13 @@
         <v>14</v>
       </c>
       <c r="C151" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>88</v>
       </c>
@@ -3619,13 +3627,13 @@
         <v>14</v>
       </c>
       <c r="C152" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>88</v>
       </c>
@@ -3633,27 +3641,27 @@
         <v>14</v>
       </c>
       <c r="C153" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>88</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C154" t="s">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>88</v>
       </c>
@@ -3661,13 +3669,13 @@
         <v>111</v>
       </c>
       <c r="C155" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>88</v>
       </c>
@@ -3675,13 +3683,13 @@
         <v>111</v>
       </c>
       <c r="C156" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>88</v>
       </c>
@@ -3689,13 +3697,13 @@
         <v>111</v>
       </c>
       <c r="C157" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>88</v>
       </c>
@@ -3703,13 +3711,13 @@
         <v>111</v>
       </c>
       <c r="C158" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>88</v>
       </c>
@@ -3717,13 +3725,13 @@
         <v>111</v>
       </c>
       <c r="C159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>88</v>
       </c>
@@ -3731,27 +3739,27 @@
         <v>111</v>
       </c>
       <c r="C160" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>88</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>316</v>
+        <v>111</v>
       </c>
       <c r="C161" t="s">
-        <v>315</v>
+        <v>117</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>88</v>
       </c>
@@ -3759,30 +3767,30 @@
         <v>316</v>
       </c>
       <c r="C162" t="s">
+        <v>315</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>88</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C163" t="s">
         <v>318</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="D163" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B163" s="2"/>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>89</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C164" t="s">
-        <v>101</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B164" s="2"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>89</v>
       </c>
@@ -3790,13 +3798,13 @@
         <v>100</v>
       </c>
       <c r="C165" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>89</v>
       </c>
@@ -3804,13 +3812,13 @@
         <v>100</v>
       </c>
       <c r="C166" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>89</v>
       </c>
@@ -3818,13 +3826,13 @@
         <v>100</v>
       </c>
       <c r="C167" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>89</v>
       </c>
@@ -3832,13 +3840,13 @@
         <v>100</v>
       </c>
       <c r="C168" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>89</v>
       </c>
@@ -3846,58 +3854,58 @@
         <v>100</v>
       </c>
       <c r="C169" t="s">
+        <v>105</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>89</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C170" t="s">
         <v>106</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="D170" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B170" s="2"/>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
-        <v>90</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C171" t="s">
-        <v>63</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B171" s="2"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>90</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C172" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>90</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>347</v>
+        <v>64</v>
       </c>
       <c r="C173" t="s">
-        <v>336</v>
+        <v>65</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>90</v>
       </c>
@@ -3905,73 +3913,73 @@
         <v>347</v>
       </c>
       <c r="C174" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>90</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C175" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>90</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C176" t="s">
+        <v>351</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>90</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C177" t="s">
         <v>354</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="D177" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B177" s="2"/>
-      <c r="D177" s="1"/>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B178" s="2"/>
+      <c r="D178" s="1"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
         <v>118</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="B179" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C179" t="s">
         <v>120</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="D179" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>320</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C180" t="s">
-        <v>322</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>320</v>
       </c>
@@ -3979,13 +3987,13 @@
         <v>321</v>
       </c>
       <c r="C181" t="s">
-        <v>323</v>
-      </c>
-      <c r="D181" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>320</v>
       </c>
@@ -3993,27 +4001,27 @@
         <v>321</v>
       </c>
       <c r="C182" t="s">
+        <v>323</v>
+      </c>
+      <c r="D182" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>320</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C183" t="s">
         <v>324</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="D183" s="1" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
-        <v>358</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C184" t="s">
-        <v>361</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>358</v>
       </c>
@@ -4021,9 +4029,23 @@
         <v>359</v>
       </c>
       <c r="C185" t="s">
+        <v>361</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>358</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C186" t="s">
         <v>363</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="D186" s="1" t="s">
         <v>362</v>
       </c>
     </row>

--- a/data/matrix_codebook.xlsx
+++ b/data/matrix_codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="645" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B42DEA66-79EC-497D-A3A4-7A12D4D2B6DD}"/>
+  <xr:revisionPtr revIDLastSave="718" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41AADE52-7C29-467C-8385-14C414329441}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1080" yWindow="1080" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="430">
   <si>
     <t>BESSI</t>
   </si>
@@ -1212,6 +1212,123 @@
   </si>
   <si>
     <t>Academic Burnout</t>
+  </si>
+  <si>
+    <t>subjectivewellbeing</t>
+  </si>
+  <si>
+    <t>Subjective wellbeing</t>
+  </si>
+  <si>
+    <t>socialanxiety</t>
+  </si>
+  <si>
+    <t>Social anxiety</t>
+  </si>
+  <si>
+    <t>mentalhealth</t>
+  </si>
+  <si>
+    <t>Mental health</t>
+  </si>
+  <si>
+    <t>socialstatus</t>
+  </si>
+  <si>
+    <t>Social status</t>
+  </si>
+  <si>
+    <t>physicalhealth</t>
+  </si>
+  <si>
+    <t>Physical health</t>
+  </si>
+  <si>
+    <t>affectivewellbeing</t>
+  </si>
+  <si>
+    <t>Affective wellbeing</t>
+  </si>
+  <si>
+    <t>BEHAVIORAL_TASKS</t>
+  </si>
+  <si>
+    <t>COOPERATION</t>
+  </si>
+  <si>
+    <t>conditionalcooperation</t>
+  </si>
+  <si>
+    <t>Conditional cooperation</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>risktaking</t>
+  </si>
+  <si>
+    <t>Risk taking</t>
+  </si>
+  <si>
+    <t>altruism</t>
+  </si>
+  <si>
+    <t>Altruism</t>
+  </si>
+  <si>
+    <t>ALTRUISM</t>
+  </si>
+  <si>
+    <t>positivereciprocity</t>
+  </si>
+  <si>
+    <t>Positive reciprocity</t>
+  </si>
+  <si>
+    <t>RECIPROCITY</t>
+  </si>
+  <si>
+    <t>Negative reciprocity</t>
+  </si>
+  <si>
+    <t>negativereciprocity</t>
+  </si>
+  <si>
+    <t>TIME-DISCOUNTING</t>
+  </si>
+  <si>
+    <t>Time discounting</t>
+  </si>
+  <si>
+    <t>timediscounting</t>
+  </si>
+  <si>
+    <t>TRUST</t>
+  </si>
+  <si>
+    <t>trust</t>
+  </si>
+  <si>
+    <t>Trust</t>
+  </si>
+  <si>
+    <t>TEAMWORK</t>
+  </si>
+  <si>
+    <t>Teamwork</t>
+  </si>
+  <si>
+    <t>teamwork</t>
+  </si>
+  <si>
+    <t>RULE-FOLLOWING</t>
+  </si>
+  <si>
+    <t>Rule Following</t>
+  </si>
+  <si>
+    <t>rulefollowing</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A8B26-530C-40CA-A676-99F1EAC2BADD}">
-  <dimension ref="A1:AO186"/>
+  <dimension ref="A1:AO203"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
@@ -3398,13 +3515,13 @@
         <v>85</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>272</v>
+        <v>392</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -3412,13 +3529,13 @@
         <v>85</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C134" t="s">
-        <v>122</v>
+        <v>401</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>273</v>
+        <v>402</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3426,13 +3543,13 @@
         <v>85</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3440,107 +3557,107 @@
         <v>85</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B137" s="2"/>
+      <c r="A137" t="s">
+        <v>85</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" t="s">
+        <v>395</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C138" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E138" t="s">
-        <v>55</v>
+        <v>274</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>85</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C139" t="s">
+        <v>67</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B140" s="2"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>86</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C139" t="s">
-        <v>79</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>86</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C140" t="s">
-        <v>345</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B141" s="2"/>
+      <c r="B141" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C141" t="s">
+        <v>54</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E141" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C142" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>57</v>
+        <v>344</v>
       </c>
       <c r="C143" t="s">
-        <v>59</v>
+        <v>345</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>279</v>
+        <v>346</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>87</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C144" t="s">
-        <v>60</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="B144" s="2"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
@@ -3550,10 +3667,10 @@
         <v>57</v>
       </c>
       <c r="C145" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -3564,10 +3681,10 @@
         <v>57</v>
       </c>
       <c r="C146" t="s">
-        <v>356</v>
+        <v>59</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>357</v>
+        <v>279</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -3575,63 +3692,63 @@
         <v>87</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>312</v>
+        <v>57</v>
       </c>
       <c r="C147" t="s">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>314</v>
+        <v>280</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B148" s="2"/>
-      <c r="D148" s="1"/>
+      <c r="A148" t="s">
+        <v>87</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C148" t="s">
+        <v>61</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B149" s="2"/>
+      <c r="A149" t="s">
+        <v>87</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C149" t="s">
+        <v>356</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>14</v>
+        <v>312</v>
       </c>
       <c r="C150" t="s">
-        <v>107</v>
+        <v>313</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>88</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C151" t="s">
-        <v>108</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>283</v>
-      </c>
+      <c r="B151" s="2"/>
+      <c r="D151" s="1"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>88</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C152" t="s">
-        <v>109</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>284</v>
-      </c>
+      <c r="B152" s="2"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
@@ -3641,10 +3758,10 @@
         <v>14</v>
       </c>
       <c r="C153" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -3655,10 +3772,10 @@
         <v>14</v>
       </c>
       <c r="C154" t="s">
-        <v>167</v>
+        <v>397</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>286</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
@@ -3666,13 +3783,13 @@
         <v>88</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C155" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -3680,13 +3797,13 @@
         <v>88</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -3694,13 +3811,13 @@
         <v>88</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C157" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -3708,13 +3825,13 @@
         <v>88</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C158" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
@@ -3722,13 +3839,13 @@
         <v>88</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>115</v>
+        <v>393</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>291</v>
+        <v>394</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -3739,10 +3856,10 @@
         <v>111</v>
       </c>
       <c r="C160" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -3753,10 +3870,10 @@
         <v>111</v>
       </c>
       <c r="C161" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -3764,13 +3881,13 @@
         <v>88</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>316</v>
+        <v>111</v>
       </c>
       <c r="C162" t="s">
-        <v>315</v>
+        <v>113</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -3778,275 +3895,488 @@
         <v>88</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>316</v>
+        <v>111</v>
       </c>
       <c r="C163" t="s">
-        <v>318</v>
+        <v>114</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B164" s="2"/>
+      <c r="A164" t="s">
+        <v>88</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C164" t="s">
+        <v>115</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C165" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C166" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>100</v>
+        <v>316</v>
       </c>
       <c r="C167" t="s">
-        <v>103</v>
+        <v>315</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>88</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C168" t="s">
+        <v>318</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B169" s="2"/>
+      <c r="D169" s="1"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B170" s="2"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
         <v>89</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B171" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C168" t="s">
-        <v>104</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>89</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C169" t="s">
-        <v>105</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>89</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C170" t="s">
-        <v>106</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B171" s="2"/>
+      <c r="C171" t="s">
+        <v>101</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="C172" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C173" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>347</v>
+        <v>100</v>
       </c>
       <c r="C174" t="s">
-        <v>336</v>
+        <v>104</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>347</v>
+        <v>100</v>
       </c>
       <c r="C175" t="s">
-        <v>348</v>
+        <v>105</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>349</v>
+        <v>298</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
+        <v>89</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C176" t="s">
+        <v>106</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B177" s="2"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
         <v>90</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C176" t="s">
-        <v>351</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>90</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C177" t="s">
-        <v>354</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B178" s="2"/>
-      <c r="D178" s="1"/>
+      <c r="B178" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C178" t="s">
+        <v>63</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="C179" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>90</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C180" t="s">
+        <v>336</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="C181" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="C182" t="s">
-        <v>323</v>
-      </c>
-      <c r="D182" t="s">
-        <v>326</v>
+        <v>351</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="C183" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>327</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>90</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C184" t="s">
+        <v>408</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>358</v>
+        <v>90</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>359</v>
+        <v>412</v>
       </c>
       <c r="C185" t="s">
-        <v>361</v>
+        <v>410</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>360</v>
+        <v>411</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
+        <v>90</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C186" t="s">
+        <v>413</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>90</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C187" t="s">
+        <v>417</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>90</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C188" t="s">
+        <v>420</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>90</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C189" t="s">
+        <v>422</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>90</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C190" t="s">
+        <v>426</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C191" t="s">
+        <v>429</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B192" s="2"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>118</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C193" t="s">
+        <v>120</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>118</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C194" t="s">
+        <v>399</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>320</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C196" t="s">
+        <v>322</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>320</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C197" t="s">
+        <v>323</v>
+      </c>
+      <c r="D197" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>320</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C198" t="s">
+        <v>324</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
         <v>358</v>
       </c>
-      <c r="B186" s="2" t="s">
+      <c r="B200" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C200" t="s">
+        <v>361</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>358</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C201" t="s">
         <v>363</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="D201" s="1" t="s">
         <v>362</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>403</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C203" t="s">
+        <v>405</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/data/matrix_codebook.xlsx
+++ b/data/matrix_codebook.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="718" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41AADE52-7C29-467C-8385-14C414329441}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1080" yWindow="1080" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="1752" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>

--- a/data/matrix_codebook.xlsx
+++ b/data/matrix_codebook.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="718" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41AADE52-7C29-467C-8385-14C414329441}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="1752" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -1657,13 +1657,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A8B26-530C-40CA-A676-99F1EAC2BADD}">
   <dimension ref="A1:AO203"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="35.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="35.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -1731,7 +1731,7 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>82</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>82</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>82</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>82</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>82</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -2288,7 +2288,7 @@
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2356,12 +2356,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>328</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>328</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>328</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>328</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>328</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>328</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>328</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>328</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>328</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>328</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>328</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>328</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>328</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>328</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>328</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>328</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>328</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>328</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>328</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>328</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>328</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>328</v>
       </c>
@@ -2669,14 +2669,14 @@
         <v>386</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B68" s="2"/>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -2956,13 +2956,13 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>83</v>
       </c>
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>83</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>83</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>83</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>83</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>83</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>83</v>
       </c>
@@ -3264,18 +3264,18 @@
         <v>266</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B113" s="2"/>
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B114" s="2"/>
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B115" s="2"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>84</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>84</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>84</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>84</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>84</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>84</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>84</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>84</v>
       </c>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G123" s="2"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>84</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>84</v>
       </c>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="J125" s="2"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>84</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>84</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>84</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>84</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>84</v>
       </c>
@@ -3493,10 +3493,10 @@
         <v>368</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B131" s="2"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>85</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>85</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>85</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>85</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>85</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>85</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>85</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>85</v>
       </c>
@@ -3608,10 +3608,10 @@
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B140" s="2"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>86</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>86</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>86</v>
       </c>
@@ -3656,10 +3656,10 @@
         <v>346</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B144" s="2"/>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>87</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>87</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>87</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>87</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>87</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>87</v>
       </c>
@@ -3743,14 +3743,14 @@
         <v>314</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B151" s="2"/>
       <c r="D151" s="1"/>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B152" s="2"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>88</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>88</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>88</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>88</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>88</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>88</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>88</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>88</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>88</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>88</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>88</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>88</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>88</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>88</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>88</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>88</v>
       </c>
@@ -3974,14 +3974,14 @@
         <v>319</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B169" s="2"/>
       <c r="D169" s="1"/>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B170" s="2"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>89</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>89</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>89</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>89</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>89</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>89</v>
       </c>
@@ -4065,10 +4065,10 @@
         <v>299</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B177" s="2"/>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>90</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>90</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>90</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>90</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>90</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>90</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>90</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>90</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>90</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>90</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>90</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>90</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>90</v>
       </c>
@@ -4250,7 +4250,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>90</v>
       </c>
@@ -4264,10 +4264,10 @@
         <v>428</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B192" s="2"/>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>118</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>118</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>320</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>320</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>320</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>358</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>358</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>403</v>
       </c>

--- a/data/matrix_codebook.xlsx
+++ b/data/matrix_codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="718" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41AADE52-7C29-467C-8385-14C414329441}"/>
+  <xr:revisionPtr revIDLastSave="774" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04A1CEC-54CF-4135-B985-D4F6C0814A9C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="448">
   <si>
     <t>BESSI</t>
   </si>
@@ -1329,6 +1329,60 @@
   </si>
   <si>
     <t>rulefollowing</t>
+  </si>
+  <si>
+    <t>Behavioural Regulation Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emotion Regulation Index </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognitive Regulation Index </t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Executive Functioning Composite </t>
+  </si>
+  <si>
+    <t>brief_behavioralregulation</t>
+  </si>
+  <si>
+    <t>brief_emotionregulation</t>
+  </si>
+  <si>
+    <t>brief_cognitiveregulation</t>
+  </si>
+  <si>
+    <t>brief_generalexecutivefunctioning</t>
+  </si>
+  <si>
+    <t>BRIEF</t>
+  </si>
+  <si>
+    <t>EXECUTIVE_FUNCTIONS</t>
+  </si>
+  <si>
+    <t>workingmemory</t>
+  </si>
+  <si>
+    <t>Working Memory</t>
+  </si>
+  <si>
+    <t>Inhibition</t>
+  </si>
+  <si>
+    <t>inhibition</t>
+  </si>
+  <si>
+    <t>flexibility</t>
+  </si>
+  <si>
+    <t>Flexibility</t>
+  </si>
+  <si>
+    <t>interferencecontrol</t>
+  </si>
+  <si>
+    <t>Interference Control</t>
   </si>
 </sst>
 </file>
@@ -1656,14 +1710,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A8B26-530C-40CA-A676-99F1EAC2BADD}">
-  <dimension ref="A1:AO203"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AO213"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="35.81640625" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="35.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -1680,7 +1734,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -1731,7 +1785,7 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -1745,7 +1799,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -1759,7 +1813,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1773,7 +1827,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1787,7 +1841,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1801,7 +1855,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -1815,7 +1869,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -1829,7 +1883,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -1843,7 +1897,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -1857,7 +1911,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -1871,7 +1925,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -1885,7 +1939,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -1899,7 +1953,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1913,7 +1967,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -1927,7 +1981,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -1941,7 +1995,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>82</v>
       </c>
@@ -1955,7 +2009,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -1969,7 +2023,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>82</v>
       </c>
@@ -1983,7 +2037,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>82</v>
       </c>
@@ -1997,7 +2051,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -2011,7 +2065,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -2025,7 +2079,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -2039,7 +2093,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -2053,7 +2107,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -2067,7 +2121,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -2081,7 +2135,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -2095,7 +2149,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -2109,7 +2163,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -2123,7 +2177,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>82</v>
       </c>
@@ -2137,7 +2191,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>82</v>
       </c>
@@ -2151,7 +2205,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -2165,7 +2219,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -2179,7 +2233,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2193,7 +2247,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -2207,7 +2261,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2221,7 +2275,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -2235,7 +2289,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -2288,7 +2342,7 @@
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -2305,7 +2359,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -2322,7 +2376,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -2339,7 +2393,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2356,12 +2410,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>328</v>
       </c>
@@ -2375,7 +2429,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>328</v>
       </c>
@@ -2389,7 +2443,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>328</v>
       </c>
@@ -2403,7 +2457,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>328</v>
       </c>
@@ -2417,7 +2471,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>328</v>
       </c>
@@ -2431,7 +2485,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>328</v>
       </c>
@@ -2445,7 +2499,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>328</v>
       </c>
@@ -2459,7 +2513,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>328</v>
       </c>
@@ -2473,7 +2527,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>328</v>
       </c>
@@ -2487,7 +2541,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>328</v>
       </c>
@@ -2501,7 +2555,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>328</v>
       </c>
@@ -2515,7 +2569,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>328</v>
       </c>
@@ -2529,7 +2583,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>328</v>
       </c>
@@ -2543,7 +2597,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>328</v>
       </c>
@@ -2557,7 +2611,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>328</v>
       </c>
@@ -2571,7 +2625,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>328</v>
       </c>
@@ -2585,7 +2639,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>328</v>
       </c>
@@ -2599,7 +2653,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>328</v>
       </c>
@@ -2613,7 +2667,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>328</v>
       </c>
@@ -2627,7 +2681,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>328</v>
       </c>
@@ -2641,7 +2695,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>328</v>
       </c>
@@ -2655,7 +2709,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>328</v>
       </c>
@@ -2669,14 +2723,14 @@
         <v>386</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B68" s="2"/>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2690,7 +2744,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2704,7 +2758,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2718,7 +2772,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2732,7 +2786,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2746,7 +2800,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2760,7 +2814,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2774,7 +2828,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2788,7 +2842,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2802,7 +2856,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2816,7 +2870,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2830,7 +2884,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2844,7 +2898,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2858,7 +2912,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -2872,7 +2926,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2886,7 +2940,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -2900,7 +2954,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -2914,7 +2968,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -2928,7 +2982,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -2942,7 +2996,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -2956,13 +3010,13 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>83</v>
       </c>
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -2976,7 +3030,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -2990,7 +3044,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -3004,7 +3058,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -3018,7 +3072,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -3032,7 +3086,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -3046,7 +3100,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -3054,7 +3108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -3068,7 +3122,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -3082,7 +3136,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -3096,7 +3150,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -3110,7 +3164,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3124,7 +3178,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3138,7 +3192,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3152,7 +3206,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3166,7 +3220,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>83</v>
       </c>
@@ -3180,7 +3234,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -3194,7 +3248,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>83</v>
       </c>
@@ -3208,7 +3262,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>83</v>
       </c>
@@ -3222,7 +3276,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>83</v>
       </c>
@@ -3236,7 +3290,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>83</v>
       </c>
@@ -3250,7 +3304,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>83</v>
       </c>
@@ -3264,18 +3318,18 @@
         <v>266</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B113" s="2"/>
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B114" s="2"/>
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B115" s="2"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>84</v>
       </c>
@@ -3292,7 +3346,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>84</v>
       </c>
@@ -3306,7 +3360,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>84</v>
       </c>
@@ -3323,7 +3377,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>84</v>
       </c>
@@ -3337,7 +3391,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>84</v>
       </c>
@@ -3351,7 +3405,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>84</v>
       </c>
@@ -3365,7 +3419,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>84</v>
       </c>
@@ -3379,7 +3433,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>84</v>
       </c>
@@ -3394,7 +3448,7 @@
       </c>
       <c r="G123" s="2"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>84</v>
       </c>
@@ -3408,7 +3462,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>84</v>
       </c>
@@ -3423,7 +3477,7 @@
       </c>
       <c r="J125" s="2"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>84</v>
       </c>
@@ -3437,7 +3491,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>84</v>
       </c>
@@ -3451,7 +3505,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>84</v>
       </c>
@@ -3465,7 +3519,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>84</v>
       </c>
@@ -3479,7 +3533,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>84</v>
       </c>
@@ -3493,10 +3547,10 @@
         <v>368</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B131" s="2"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>85</v>
       </c>
@@ -3510,7 +3564,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>85</v>
       </c>
@@ -3524,7 +3578,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>85</v>
       </c>
@@ -3538,7 +3592,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>85</v>
       </c>
@@ -3552,7 +3606,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>85</v>
       </c>
@@ -3566,7 +3620,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>85</v>
       </c>
@@ -3580,7 +3634,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>85</v>
       </c>
@@ -3594,7 +3648,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>85</v>
       </c>
@@ -3608,10 +3662,10 @@
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B140" s="2"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>86</v>
       </c>
@@ -3628,7 +3682,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>86</v>
       </c>
@@ -3642,7 +3696,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>86</v>
       </c>
@@ -3656,10 +3710,10 @@
         <v>346</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B144" s="2"/>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>87</v>
       </c>
@@ -3673,7 +3727,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>87</v>
       </c>
@@ -3687,7 +3741,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>87</v>
       </c>
@@ -3701,7 +3755,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>87</v>
       </c>
@@ -3715,7 +3769,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>87</v>
       </c>
@@ -3729,7 +3783,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>87</v>
       </c>
@@ -3743,14 +3797,14 @@
         <v>314</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B151" s="2"/>
       <c r="D151" s="1"/>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B152" s="2"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>88</v>
       </c>
@@ -3764,7 +3818,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>88</v>
       </c>
@@ -3778,7 +3832,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>88</v>
       </c>
@@ -3792,7 +3846,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>88</v>
       </c>
@@ -3806,7 +3860,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>88</v>
       </c>
@@ -3820,7 +3874,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>88</v>
       </c>
@@ -3834,7 +3888,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>88</v>
       </c>
@@ -3848,7 +3902,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>88</v>
       </c>
@@ -3862,7 +3916,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>88</v>
       </c>
@@ -3876,7 +3930,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>88</v>
       </c>
@@ -3890,7 +3944,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>88</v>
       </c>
@@ -3904,7 +3958,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>88</v>
       </c>
@@ -3918,7 +3972,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>88</v>
       </c>
@@ -3932,7 +3986,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>88</v>
       </c>
@@ -3946,7 +4000,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>88</v>
       </c>
@@ -3960,7 +4014,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>88</v>
       </c>
@@ -3974,14 +4028,14 @@
         <v>319</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B169" s="2"/>
       <c r="D169" s="1"/>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B170" s="2"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>89</v>
       </c>
@@ -3995,7 +4049,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>89</v>
       </c>
@@ -4009,7 +4063,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>89</v>
       </c>
@@ -4023,7 +4077,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>89</v>
       </c>
@@ -4037,7 +4091,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>89</v>
       </c>
@@ -4051,7 +4105,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>89</v>
       </c>
@@ -4065,10 +4119,10 @@
         <v>299</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B177" s="2"/>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>90</v>
       </c>
@@ -4082,7 +4136,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>90</v>
       </c>
@@ -4096,7 +4150,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>90</v>
       </c>
@@ -4110,7 +4164,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>90</v>
       </c>
@@ -4124,7 +4178,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>90</v>
       </c>
@@ -4138,7 +4192,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>90</v>
       </c>
@@ -4152,7 +4206,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>90</v>
       </c>
@@ -4166,7 +4220,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>90</v>
       </c>
@@ -4180,7 +4234,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>90</v>
       </c>
@@ -4194,7 +4248,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>90</v>
       </c>
@@ -4208,7 +4262,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>90</v>
       </c>
@@ -4222,7 +4276,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>90</v>
       </c>
@@ -4236,7 +4290,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>90</v>
       </c>
@@ -4250,7 +4304,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>90</v>
       </c>
@@ -4264,10 +4318,10 @@
         <v>428</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B192" s="2"/>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>118</v>
       </c>
@@ -4281,7 +4335,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>118</v>
       </c>
@@ -4295,7 +4349,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>320</v>
       </c>
@@ -4309,7 +4363,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>320</v>
       </c>
@@ -4323,7 +4377,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>320</v>
       </c>
@@ -4337,45 +4391,165 @@
         <v>327</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B199" s="2"/>
+      <c r="D199" s="1"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
+        <v>320</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C200" t="s">
+        <v>434</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>320</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C201" t="s">
+        <v>435</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>320</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C202" t="s">
+        <v>436</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>320</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C203" t="s">
+        <v>437</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B204" s="2"/>
+      <c r="D204" s="1"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>320</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C205" t="s">
+        <v>440</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>320</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C206" t="s">
+        <v>443</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>320</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C207" t="s">
+        <v>444</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>320</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C208" t="s">
+        <v>446</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
         <v>358</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="B210" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C200" t="s">
+      <c r="C210" t="s">
         <v>361</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="D210" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
         <v>358</v>
       </c>
-      <c r="B201" s="2" t="s">
+      <c r="B211" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C211" t="s">
         <v>363</v>
       </c>
-      <c r="D201" s="1" t="s">
+      <c r="D211" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
         <v>403</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B213" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C213" t="s">
         <v>405</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="D213" s="1" t="s">
         <v>406</v>
       </c>
     </row>

--- a/data/matrix_codebook.xlsx
+++ b/data/matrix_codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="774" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04A1CEC-54CF-4135-B985-D4F6C0814A9C}"/>
+  <xr:revisionPtr revIDLastSave="779" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B694BAE7-DA28-4343-B94F-FD04171EE49B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="451">
   <si>
     <t>BESSI</t>
   </si>
@@ -1383,6 +1383,15 @@
   </si>
   <si>
     <t>Interference Control</t>
+  </si>
+  <si>
+    <t>SELF-ESTEEM</t>
+  </si>
+  <si>
+    <t>selfesteem</t>
+  </si>
+  <si>
+    <t>Self-esteem</t>
   </si>
 </sst>
 </file>
@@ -1710,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A8B26-530C-40CA-A676-99F1EAC2BADD}">
-  <dimension ref="A1:AO213"/>
+  <dimension ref="A1:AO214"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
@@ -4141,13 +4150,13 @@
         <v>90</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>64</v>
+        <v>448</v>
       </c>
       <c r="C179" t="s">
-        <v>65</v>
+        <v>449</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>301</v>
+        <v>450</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
@@ -4155,13 +4164,13 @@
         <v>90</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>347</v>
+        <v>64</v>
       </c>
       <c r="C180" t="s">
-        <v>336</v>
+        <v>65</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>337</v>
+        <v>301</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
@@ -4172,10 +4181,10 @@
         <v>347</v>
       </c>
       <c r="C181" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
@@ -4183,13 +4192,13 @@
         <v>90</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C182" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
@@ -4197,13 +4206,13 @@
         <v>90</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C183" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -4211,13 +4220,13 @@
         <v>90</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>407</v>
+        <v>353</v>
       </c>
       <c r="C184" t="s">
-        <v>408</v>
+        <v>354</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>409</v>
+        <v>355</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
@@ -4225,13 +4234,13 @@
         <v>90</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C185" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -4239,13 +4248,13 @@
         <v>90</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C186" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
@@ -4256,10 +4265,10 @@
         <v>415</v>
       </c>
       <c r="C187" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
@@ -4267,13 +4276,13 @@
         <v>90</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C188" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -4281,13 +4290,13 @@
         <v>90</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C189" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
@@ -4295,13 +4304,13 @@
         <v>90</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C190" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
@@ -4309,31 +4318,31 @@
         <v>90</v>
       </c>
       <c r="B191" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C191" t="s">
+        <v>426</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>90</v>
+      </c>
+      <c r="B192" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C192" t="s">
         <v>429</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="D192" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B192" s="2"/>
-    </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
-        <v>118</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C193" t="s">
-        <v>120</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>302</v>
-      </c>
+      <c r="B193" s="2"/>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
@@ -4343,24 +4352,24 @@
         <v>119</v>
       </c>
       <c r="C194" t="s">
+        <v>120</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>118</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C195" t="s">
         <v>399</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>320</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C196" t="s">
-        <v>322</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
@@ -4371,10 +4380,10 @@
         <v>321</v>
       </c>
       <c r="C197" t="s">
-        <v>323</v>
-      </c>
-      <c r="D197" t="s">
-        <v>326</v>
+        <v>322</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -4385,29 +4394,29 @@
         <v>321</v>
       </c>
       <c r="C198" t="s">
+        <v>323</v>
+      </c>
+      <c r="D198" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>320</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C199" t="s">
         <v>324</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B199" s="2"/>
-      <c r="D199" s="1"/>
-    </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>320</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C200" t="s">
-        <v>434</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>430</v>
-      </c>
+      <c r="B200" s="2"/>
+      <c r="D200" s="1"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
@@ -4417,10 +4426,10 @@
         <v>438</v>
       </c>
       <c r="C201" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -4431,10 +4440,10 @@
         <v>438</v>
       </c>
       <c r="C202" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
@@ -4445,29 +4454,29 @@
         <v>438</v>
       </c>
       <c r="C203" t="s">
+        <v>436</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>320</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C204" t="s">
         <v>437</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="D204" s="1" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B204" s="2"/>
-      <c r="D204" s="1"/>
-    </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>320</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C205" t="s">
-        <v>440</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>441</v>
-      </c>
+      <c r="B205" s="2"/>
+      <c r="D205" s="1"/>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
@@ -4477,10 +4486,10 @@
         <v>439</v>
       </c>
       <c r="C206" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
@@ -4491,10 +4500,10 @@
         <v>439</v>
       </c>
       <c r="C207" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
@@ -4505,24 +4514,24 @@
         <v>439</v>
       </c>
       <c r="C208" t="s">
+        <v>444</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>320</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C209" t="s">
         <v>446</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="D209" s="1" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>358</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C210" t="s">
-        <v>361</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
@@ -4533,23 +4542,37 @@
         <v>359</v>
       </c>
       <c r="C211" t="s">
+        <v>361</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>358</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C212" t="s">
         <v>363</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="D212" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
         <v>403</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="B214" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C214" t="s">
         <v>405</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="D214" s="1" t="s">
         <v>406</v>
       </c>
     </row>

--- a/data/matrix_codebook.xlsx
+++ b/data/matrix_codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="779" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B694BAE7-DA28-4343-B94F-FD04171EE49B}"/>
+  <xr:revisionPtr revIDLastSave="845" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5466AC2F-965B-4439-BC55-0AA140202DDC}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="490">
   <si>
     <t>BESSI</t>
   </si>
@@ -1392,6 +1392,123 @@
   </si>
   <si>
     <t>Self-esteem</t>
+  </si>
+  <si>
+    <t>positiveaffect</t>
+  </si>
+  <si>
+    <t>negativeaffect</t>
+  </si>
+  <si>
+    <t>Positive affect</t>
+  </si>
+  <si>
+    <t>Negative affect</t>
+  </si>
+  <si>
+    <t>distressintolerance</t>
+  </si>
+  <si>
+    <t>Distress intolerance</t>
+  </si>
+  <si>
+    <t>INTOLERANCE</t>
+  </si>
+  <si>
+    <t>BELIEFS</t>
+  </si>
+  <si>
+    <t>Emotion Controllability</t>
+  </si>
+  <si>
+    <t>emotioncontrollability</t>
+  </si>
+  <si>
+    <t>CONTEXT</t>
+  </si>
+  <si>
+    <t>SITUATION_FEATURES</t>
+  </si>
+  <si>
+    <t>pleasantsituation</t>
+  </si>
+  <si>
+    <t>familiarsituation</t>
+  </si>
+  <si>
+    <t>controllablesituation</t>
+  </si>
+  <si>
+    <t>socialsituation</t>
+  </si>
+  <si>
+    <t>sociallywarmsituation</t>
+  </si>
+  <si>
+    <t>sociallydominantsituation</t>
+  </si>
+  <si>
+    <t>CONTEXTUAL_BEHAVIORS</t>
+  </si>
+  <si>
+    <t>emotionregulationinitiation</t>
+  </si>
+  <si>
+    <t>emotionregulationinitiationfrequency</t>
+  </si>
+  <si>
+    <t>Pleasant situation</t>
+  </si>
+  <si>
+    <t>Familiar situation</t>
+  </si>
+  <si>
+    <t>Social situation</t>
+  </si>
+  <si>
+    <t>Controllable situation</t>
+  </si>
+  <si>
+    <t>Socially warm situation</t>
+  </si>
+  <si>
+    <t>Socially dominant situation</t>
+  </si>
+  <si>
+    <t>Emotion regulationi initiation</t>
+  </si>
+  <si>
+    <t>Emotion regulation initiation frequency</t>
+  </si>
+  <si>
+    <t>CHANGE</t>
+  </si>
+  <si>
+    <t>VOLITIONAL_CHANGE</t>
+  </si>
+  <si>
+    <t>preferenceforhumanvsdigital</t>
+  </si>
+  <si>
+    <t>willingnessfordigitalassistance</t>
+  </si>
+  <si>
+    <t>useofdigitalassistance</t>
+  </si>
+  <si>
+    <t>changegoals</t>
+  </si>
+  <si>
+    <t>Change goals</t>
+  </si>
+  <si>
+    <t>Preference for human vs digital assistance for change</t>
+  </si>
+  <si>
+    <t>Willingness for digital assistance for change</t>
+  </si>
+  <si>
+    <t>Use of digital assistance for change</t>
   </si>
 </sst>
 </file>
@@ -1719,14 +1836,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A8B26-530C-40CA-A676-99F1EAC2BADD}">
-  <dimension ref="A1:AO214"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AO234"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="35.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="35.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -1743,7 +1860,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -1794,7 +1911,7 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -1808,7 +1925,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -1822,7 +1939,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1836,7 +1953,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1850,7 +1967,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1864,7 +1981,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -1878,7 +1995,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -1892,7 +2009,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -1906,7 +2023,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -1920,7 +2037,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -1934,7 +2051,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -1948,7 +2065,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -1962,7 +2079,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1976,7 +2093,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -1990,7 +2107,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -2004,7 +2121,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>82</v>
       </c>
@@ -2018,7 +2135,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -2032,7 +2149,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>82</v>
       </c>
@@ -2046,7 +2163,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>82</v>
       </c>
@@ -2060,7 +2177,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -2074,7 +2191,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -2088,7 +2205,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -2102,7 +2219,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -2116,7 +2233,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -2130,7 +2247,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -2144,7 +2261,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -2158,7 +2275,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -2172,7 +2289,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -2186,7 +2303,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>82</v>
       </c>
@@ -2200,7 +2317,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>82</v>
       </c>
@@ -2214,7 +2331,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -2228,7 +2345,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -2242,7 +2359,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2256,7 +2373,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -2270,7 +2387,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2284,7 +2401,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -2298,7 +2415,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -2351,7 +2468,7 @@
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -2368,7 +2485,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -2385,7 +2502,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -2402,7 +2519,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2419,12 +2536,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>328</v>
       </c>
@@ -2438,7 +2555,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>328</v>
       </c>
@@ -2452,7 +2569,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>328</v>
       </c>
@@ -2466,7 +2583,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>328</v>
       </c>
@@ -2480,7 +2597,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>328</v>
       </c>
@@ -2494,7 +2611,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>328</v>
       </c>
@@ -2508,7 +2625,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>328</v>
       </c>
@@ -2522,7 +2639,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>328</v>
       </c>
@@ -2536,7 +2653,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>328</v>
       </c>
@@ -2550,7 +2667,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>328</v>
       </c>
@@ -2564,7 +2681,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>328</v>
       </c>
@@ -2578,7 +2695,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>328</v>
       </c>
@@ -2592,7 +2709,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>328</v>
       </c>
@@ -2606,7 +2723,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>328</v>
       </c>
@@ -2620,7 +2737,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>328</v>
       </c>
@@ -2634,7 +2751,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>328</v>
       </c>
@@ -2648,7 +2765,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>328</v>
       </c>
@@ -2662,7 +2779,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>328</v>
       </c>
@@ -2676,7 +2793,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>328</v>
       </c>
@@ -2690,7 +2807,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>328</v>
       </c>
@@ -2704,7 +2821,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>328</v>
       </c>
@@ -2718,7 +2835,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>328</v>
       </c>
@@ -2732,14 +2849,14 @@
         <v>386</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B68" s="2"/>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2753,7 +2870,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2767,7 +2884,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2781,7 +2898,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2795,7 +2912,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2809,7 +2926,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2823,7 +2940,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2837,7 +2954,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2851,7 +2968,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2865,7 +2982,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2879,7 +2996,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -2893,7 +3010,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2907,7 +3024,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2921,7 +3038,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -2935,7 +3052,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2949,7 +3066,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -2963,7 +3080,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -2977,7 +3094,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -2991,7 +3108,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -3005,7 +3122,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -3019,13 +3136,13 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>83</v>
       </c>
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3039,7 +3156,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3053,7 +3170,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -3067,7 +3184,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -3081,7 +3198,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -3095,7 +3212,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -3109,7 +3226,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -3117,7 +3234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -3131,7 +3248,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -3145,7 +3262,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -3159,7 +3276,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -3173,7 +3290,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3187,7 +3304,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3201,7 +3318,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3215,7 +3332,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3229,7 +3346,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>83</v>
       </c>
@@ -3243,7 +3360,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -3257,7 +3374,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>83</v>
       </c>
@@ -3271,7 +3388,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>83</v>
       </c>
@@ -3285,7 +3402,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>83</v>
       </c>
@@ -3299,7 +3416,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>83</v>
       </c>
@@ -3313,7 +3430,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>83</v>
       </c>
@@ -3327,18 +3444,18 @@
         <v>266</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B113" s="2"/>
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B114" s="2"/>
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B115" s="2"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>84</v>
       </c>
@@ -3355,7 +3472,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>84</v>
       </c>
@@ -3369,7 +3486,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>84</v>
       </c>
@@ -3386,7 +3503,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>84</v>
       </c>
@@ -3400,7 +3517,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>84</v>
       </c>
@@ -3414,7 +3531,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>84</v>
       </c>
@@ -3428,7 +3545,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>84</v>
       </c>
@@ -3442,7 +3559,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>84</v>
       </c>
@@ -3457,7 +3574,7 @@
       </c>
       <c r="G123" s="2"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>84</v>
       </c>
@@ -3471,7 +3588,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>84</v>
       </c>
@@ -3486,7 +3603,7 @@
       </c>
       <c r="J125" s="2"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>84</v>
       </c>
@@ -3500,7 +3617,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>84</v>
       </c>
@@ -3514,7 +3631,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>84</v>
       </c>
@@ -3528,7 +3645,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>84</v>
       </c>
@@ -3542,7 +3659,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>84</v>
       </c>
@@ -3556,10 +3673,10 @@
         <v>368</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B131" s="2"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>85</v>
       </c>
@@ -3573,7 +3690,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>85</v>
       </c>
@@ -3587,7 +3704,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>85</v>
       </c>
@@ -3601,35 +3718,35 @@
         <v>402</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>85</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C135" t="s">
-        <v>121</v>
+        <v>451</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>85</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C136" t="s">
-        <v>122</v>
+        <v>452</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>85</v>
       </c>
@@ -3637,148 +3754,138 @@
         <v>13</v>
       </c>
       <c r="C137" t="s">
-        <v>395</v>
+        <v>121</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>85</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>85</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C139" t="s">
+        <v>395</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>85</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C140" t="s">
+        <v>66</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>85</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C141" t="s">
         <v>67</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B140" s="2"/>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>85</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C142" t="s">
+        <v>455</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B143" s="2"/>
+      <c r="D143" s="1"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B144" s="2"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
         <v>86</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B145" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C145" t="s">
         <v>54</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D145" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E145" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
         <v>86</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B146" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C146" t="s">
         <v>79</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
         <v>86</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B147" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C147" t="s">
         <v>345</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D147" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B144" s="2"/>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>87</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C145" t="s">
-        <v>58</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>87</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C146" t="s">
-        <v>59</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>87</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C147" t="s">
-        <v>60</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>87</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C148" t="s">
-        <v>61</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B148" s="2"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>87</v>
       </c>
@@ -3786,90 +3893,90 @@
         <v>57</v>
       </c>
       <c r="C149" t="s">
-        <v>356</v>
+        <v>58</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>87</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C150" t="s">
+        <v>59</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>87</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C151" t="s">
+        <v>60</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>87</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C152" t="s">
+        <v>61</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>87</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C153" t="s">
+        <v>356</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>87</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C154" t="s">
         <v>313</v>
       </c>
-      <c r="D150" s="1" t="s">
+      <c r="D154" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B151" s="2"/>
-      <c r="D151" s="1"/>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B152" s="2"/>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>88</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C153" t="s">
-        <v>107</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>88</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C154" t="s">
-        <v>397</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>88</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C155" t="s">
-        <v>108</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>88</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C156" t="s">
-        <v>109</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B155" s="2"/>
+      <c r="D155" s="1"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B156" s="2"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>88</v>
       </c>
@@ -3877,13 +3984,13 @@
         <v>14</v>
       </c>
       <c r="C157" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>88</v>
       </c>
@@ -3891,13 +3998,13 @@
         <v>14</v>
       </c>
       <c r="C158" t="s">
-        <v>167</v>
+        <v>397</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>88</v>
       </c>
@@ -3905,69 +4012,69 @@
         <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>393</v>
+        <v>108</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>88</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C160" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>88</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C161" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>88</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>88</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C163" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>88</v>
       </c>
@@ -3975,13 +4082,13 @@
         <v>111</v>
       </c>
       <c r="C164" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>88</v>
       </c>
@@ -3989,13 +4096,13 @@
         <v>111</v>
       </c>
       <c r="C165" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>88</v>
       </c>
@@ -4003,104 +4110,104 @@
         <v>111</v>
       </c>
       <c r="C166" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>88</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>316</v>
+        <v>111</v>
       </c>
       <c r="C167" t="s">
-        <v>315</v>
+        <v>114</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>88</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C168" t="s">
+        <v>115</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>88</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C169" t="s">
+        <v>116</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>88</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C170" t="s">
+        <v>117</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>88</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C171" t="s">
+        <v>315</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>88</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C172" t="s">
         <v>318</v>
       </c>
-      <c r="D168" s="1" t="s">
+      <c r="D172" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B169" s="2"/>
-      <c r="D169" s="1"/>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B170" s="2"/>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>89</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C171" t="s">
-        <v>101</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>89</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C172" t="s">
-        <v>102</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>89</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C173" t="s">
-        <v>103</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>89</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C174" t="s">
-        <v>104</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B173" s="2"/>
+      <c r="D173" s="1"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B174" s="2"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>89</v>
       </c>
@@ -4108,13 +4215,13 @@
         <v>100</v>
       </c>
       <c r="C175" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>89</v>
       </c>
@@ -4122,458 +4229,696 @@
         <v>100</v>
       </c>
       <c r="C176" t="s">
+        <v>102</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>89</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C177" t="s">
+        <v>103</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>89</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C178" t="s">
+        <v>104</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>89</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C179" t="s">
+        <v>105</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>89</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C180" t="s">
         <v>106</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="D180" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B177" s="2"/>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>90</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C178" t="s">
-        <v>63</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>90</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C179" t="s">
-        <v>449</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
-        <v>90</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C180" t="s">
-        <v>65</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
-        <v>90</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C181" t="s">
-        <v>336</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B181" s="2"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>90</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>347</v>
+        <v>62</v>
       </c>
       <c r="C182" t="s">
-        <v>348</v>
+        <v>63</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>90</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>350</v>
+        <v>448</v>
       </c>
       <c r="C183" t="s">
-        <v>351</v>
+        <v>449</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>90</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>353</v>
+        <v>64</v>
       </c>
       <c r="C184" t="s">
-        <v>354</v>
+        <v>65</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>90</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>407</v>
+        <v>347</v>
       </c>
       <c r="C185" t="s">
-        <v>408</v>
+        <v>336</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>90</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>412</v>
+        <v>347</v>
       </c>
       <c r="C186" t="s">
-        <v>410</v>
+        <v>348</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>90</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="C187" t="s">
-        <v>413</v>
+        <v>351</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>90</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>415</v>
+        <v>353</v>
       </c>
       <c r="C188" t="s">
-        <v>417</v>
+        <v>354</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>90</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="C189" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>90</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C190" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>90</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C191" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>90</v>
       </c>
       <c r="B192" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C192" t="s">
+        <v>417</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>90</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C193" t="s">
+        <v>420</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>90</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C194" t="s">
+        <v>422</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>90</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C195" t="s">
+        <v>426</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>90</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C196" t="s">
         <v>429</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="D196" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B193" s="2"/>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B197" s="2"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
         <v>118</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B198" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C198" t="s">
         <v>120</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="D198" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
         <v>118</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="B199" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C195" t="s">
+      <c r="C199" t="s">
         <v>399</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>320</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C197" t="s">
-        <v>322</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>320</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C198" t="s">
-        <v>323</v>
-      </c>
-      <c r="D198" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>320</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C199" t="s">
-        <v>324</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B200" s="2"/>
-      <c r="D200" s="1"/>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>320</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>438</v>
+        <v>321</v>
       </c>
       <c r="C201" t="s">
-        <v>434</v>
+        <v>322</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>320</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>438</v>
+        <v>321</v>
       </c>
       <c r="C202" t="s">
-        <v>435</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+      <c r="D202" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>320</v>
       </c>
       <c r="B203" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C203" t="s">
+        <v>324</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B204" s="2"/>
+      <c r="D204" s="1"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>320</v>
+      </c>
+      <c r="B205" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C203" t="s">
-        <v>436</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>320</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C204" t="s">
-        <v>437</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B205" s="2"/>
-      <c r="D205" s="1"/>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C205" t="s">
+        <v>434</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>320</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C206" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>320</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C207" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>320</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C208" t="s">
+        <v>437</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B209" s="2"/>
+      <c r="D209" s="1"/>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>320</v>
+      </c>
+      <c r="B210" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C210" t="s">
+        <v>440</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>320</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C211" t="s">
+        <v>443</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>320</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C212" t="s">
         <v>444</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="D212" s="1" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
         <v>320</v>
       </c>
-      <c r="B209" s="2" t="s">
+      <c r="B213" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C213" t="s">
         <v>446</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="D213" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
         <v>358</v>
       </c>
-      <c r="B211" s="2" t="s">
+      <c r="B215" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C215" t="s">
         <v>361</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="D215" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
         <v>358</v>
       </c>
-      <c r="B212" s="2" t="s">
+      <c r="B216" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C212" t="s">
+      <c r="C216" t="s">
         <v>363</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="D216" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
         <v>403</v>
       </c>
-      <c r="B214" s="2" t="s">
+      <c r="B218" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C218" t="s">
         <v>405</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="D218" s="1" t="s">
         <v>406</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>458</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C220" t="s">
+        <v>460</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>461</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C222" t="s">
+        <v>463</v>
+      </c>
+      <c r="D222" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>461</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C223" t="s">
+        <v>464</v>
+      </c>
+      <c r="D223" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>461</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C224" t="s">
+        <v>465</v>
+      </c>
+      <c r="D224" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>461</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C225" t="s">
+        <v>466</v>
+      </c>
+      <c r="D225" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>461</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C226" t="s">
+        <v>467</v>
+      </c>
+      <c r="D226" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>461</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C227" t="s">
+        <v>468</v>
+      </c>
+      <c r="D227" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>461</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C228" t="s">
+        <v>470</v>
+      </c>
+      <c r="D228" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>461</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C229" t="s">
+        <v>471</v>
+      </c>
+      <c r="D229" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>480</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C231" t="s">
+        <v>485</v>
+      </c>
+      <c r="D231" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>480</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C232" t="s">
+        <v>482</v>
+      </c>
+      <c r="D232" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>480</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C233" t="s">
+        <v>483</v>
+      </c>
+      <c r="D233" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>480</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C234" t="s">
+        <v>484</v>
+      </c>
+      <c r="D234" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>
